--- a/Archivio/Setup/Origine.xlsx
+++ b/Archivio/Setup/Origine.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Normalizza\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F3B03B-5DE0-468A-A97F-2FCE744D6A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883DECC-2E44-442B-A0C2-F981F4A64230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="61">
   <si>
     <t>DbInp</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>RES Timesheet Extract</t>
+  </si>
+  <si>
+    <t>Working Hours by Day</t>
   </si>
 </sst>
 </file>
@@ -881,7 +884,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>

--- a/Archivio/Setup/Origine.xlsx
+++ b/Archivio/Setup/Origine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883DECC-2E44-442B-A0C2-F981F4A64230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A465D50-E3C2-4F51-AD4E-74D3E226318D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="57">
   <si>
     <t>DbInp</t>
   </si>
@@ -72,12 +72,6 @@
     <t>fte_mese</t>
   </si>
   <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>key_global</t>
-  </si>
-  <si>
     <t>Org</t>
   </si>
   <si>
@@ -94,12 +88,6 @@
   </si>
   <si>
     <t>pbx_all_project_mapped_power_bi_column_set</t>
-  </si>
-  <si>
-    <t>PBX_Key</t>
-  </si>
-  <si>
-    <t>pbx_key</t>
   </si>
   <si>
     <t>PBX_PV_Total</t>
@@ -525,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -850,13 +838,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
         <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -864,7 +852,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
@@ -880,105 +868,71 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
       <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
         <v>50</v>
-      </c>
-      <c r="F22" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>56</v>
-      </c>
       <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" t="s">
         <v>50</v>
-      </c>
-      <c r="E26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Archivio/Setup/Origine.xlsx
+++ b/Archivio/Setup/Origine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A465D50-E3C2-4F51-AD4E-74D3E226318D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B2A073-FFB1-41C9-A667-EF07F53DD465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
   <si>
     <t>DbInp</t>
   </si>
@@ -60,9 +60,6 @@
     <t>01_tabella_data</t>
   </si>
   <si>
-    <t>All Project Mapped - Power BI Column Set</t>
-  </si>
-  <si>
     <t>all_project_mapped_power_bi_column_set</t>
   </si>
   <si>
@@ -84,24 +81,12 @@
     <t>outs_ore_mese</t>
   </si>
   <si>
-    <t>PBX_ AllProjectMappedPowerBIColumnSet</t>
-  </si>
-  <si>
-    <t>pbx_all_project_mapped_power_bi_column_set</t>
-  </si>
-  <si>
     <t>PBX_PV_Total</t>
   </si>
   <si>
     <t>pbx_pv_total</t>
   </si>
   <si>
-    <t>PBX_TimesheetInformationByMonth</t>
-  </si>
-  <si>
-    <t>pbx_timesheet_information_by_month</t>
-  </si>
-  <si>
     <t>PV_Date</t>
   </si>
   <si>
@@ -144,9 +129,6 @@
     <t>standard_activities</t>
   </si>
   <si>
-    <t>Timesheet Information By Month</t>
-  </si>
-  <si>
     <t>timesheet_information_by_month</t>
   </si>
   <si>
@@ -196,6 +178,12 @@
   </si>
   <si>
     <t>Working Hours by Day</t>
+  </si>
+  <si>
+    <t>PV_Total_Outs</t>
+  </si>
+  <si>
+    <t>pv_total_outs</t>
   </si>
 </sst>
 </file>
@@ -513,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -566,13 +554,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -583,13 +571,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -600,13 +588,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -617,13 +605,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -634,13 +622,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -651,13 +639,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -668,13 +656,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -685,13 +673,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -702,13 +690,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -719,13 +707,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -736,13 +724,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -753,13 +741,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
@@ -770,13 +758,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
@@ -787,13 +775,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
@@ -801,7 +789,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
         <v>39</v>
@@ -817,122 +805,71 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
       <c r="B18" t="s">
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
         <v>42</v>
       </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
       <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
         <v>43</v>
       </c>
-      <c r="F19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="F20" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
         <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Archivio/Setup/Origine.xlsx
+++ b/Archivio/Setup/Origine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B2A073-FFB1-41C9-A667-EF07F53DD465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2236D50-4F71-4690-BE88-DC6FD351B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
   <si>
     <t>DbInp</t>
   </si>
@@ -178,12 +178,6 @@
   </si>
   <si>
     <t>Working Hours by Day</t>
-  </si>
-  <si>
-    <t>PV_Total_Outs</t>
-  </si>
-  <si>
-    <t>pv_total_outs</t>
   </si>
 </sst>
 </file>
@@ -501,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -772,103 +766,86 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" t="s">
         <v>44</v>
       </c>
     </row>

--- a/Archivio/Setup/Origine.xlsx
+++ b/Archivio/Setup/Origine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2236D50-4F71-4690-BE88-DC6FD351B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F68E3B8-33F7-4063-8222-DEECF18FD33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="47">
   <si>
     <t>DbInp</t>
   </si>
@@ -75,12 +75,6 @@
     <t>org</t>
   </si>
   <si>
-    <t>Outs_Ore_Mese</t>
-  </si>
-  <si>
-    <t>outs_ore_mese</t>
-  </si>
-  <si>
     <t>PBX_PV_Total</t>
   </si>
   <si>
@@ -97,12 +91,6 @@
   </si>
   <si>
     <t>pv_total</t>
-  </si>
-  <si>
-    <t>Pv_Total_OutsOreMese</t>
-  </si>
-  <si>
-    <t>pv_total_outs_ore_mese</t>
   </si>
   <si>
     <t>Resource Type</t>
@@ -495,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -701,13 +689,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -718,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -732,7 +720,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
@@ -748,105 +736,71 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
       <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
         <v>40</v>
-      </c>
-      <c r="F16" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
         <v>40</v>
-      </c>
-      <c r="E20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
